--- a/AAII_Financials/Quarterly/YLDGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YLDGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>YLDGY</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -670,55 +670,70 @@
     <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,8 +767,20 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +814,20 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +861,20 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +888,12 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +927,20 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +974,20 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -942,8 +1021,20 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1068,20 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,8 +1092,12 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1024,8 +1131,20 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1059,8 +1178,20 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1205,12 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1109,8 +1244,20 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1144,8 +1291,20 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,8 +1338,20 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1214,8 +1385,20 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1432,20 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,8 +1479,20 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1319,8 +1526,20 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1354,8 +1573,20 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1620,20 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1667,20 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1714,20 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1761,20 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1529,8 +1808,20 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1564,8 +1855,20 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1902,20 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1634,48 +1949,72 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +2028,12 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,288 +2047,388 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>843600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>830800</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1043100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1024900</v>
+      </c>
+      <c r="H41" s="3">
         <v>1166600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>1151700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>1396100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>1452800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>1464500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>1473900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>1834400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>1782700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>2687800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>2837700</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>4100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="I42" s="3">
         <v>4100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>2500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>2500</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1666000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1640800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1695100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1665400</v>
+      </c>
+      <c r="H43" s="3">
         <v>2153600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>2126100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>2535200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>2638100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>3015600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>3035000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>3276100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>3183700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>3720400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>3927800</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2955600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2910800</v>
+      </c>
+      <c r="F44" s="3">
+        <v>3361200</v>
+      </c>
+      <c r="G44" s="3">
+        <v>3302300</v>
+      </c>
+      <c r="H44" s="3">
         <v>3468100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="I44" s="3">
         <v>3423800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>4340000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>4516000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>6239900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>6280000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>8313700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>8079400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>11032600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>11647900</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>305900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>301300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>278800</v>
+      </c>
+      <c r="G45" s="3">
+        <v>274000</v>
+      </c>
+      <c r="H45" s="3">
         <v>252900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>249700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>225700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="K45" s="3">
         <v>234800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>361300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>363600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>390300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>379300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>583500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>616000</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5775400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5687800</v>
+      </c>
+      <c r="F46" s="3">
+        <v>6378300</v>
+      </c>
+      <c r="G46" s="3">
+        <v>6266500</v>
+      </c>
+      <c r="H46" s="3">
         <v>7045400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>6955400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>8497000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>8841700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>11083800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>11155000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>13814500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>13425000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>18024900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>19030200</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1165900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1148200</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1204400</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1183300</v>
+      </c>
+      <c r="H47" s="3">
         <v>1191900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="I47" s="3">
         <v>1176700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="J47" s="3">
         <v>1207000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="K47" s="3">
         <v>1256000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>1192300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>1199900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>1261600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>1226000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>1498900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>1582500</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>428200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>421700</v>
+      </c>
+      <c r="F48" s="3">
+        <v>445200</v>
+      </c>
+      <c r="G48" s="3">
+        <v>437400</v>
+      </c>
+      <c r="H48" s="3">
         <v>462800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>456900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>471000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>490100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>483500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>486700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>509300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>495000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>493600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>521100</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2019,8 +2462,20 @@
       <c r="M49" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>300</v>
+      </c>
+      <c r="O49" s="3">
+        <v>300</v>
+      </c>
+      <c r="P49" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2509,20 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2556,67 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6042500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5950800</v>
+      </c>
+      <c r="F52" s="3">
+        <v>5849200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>5746700</v>
+      </c>
+      <c r="H52" s="3">
         <v>5886100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>5810900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>5601100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>5828400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>5848200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>5885800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>5968000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>5766900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>5366000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>5665200</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2650,67 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13463100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13259000</v>
+      </c>
+      <c r="F54" s="3">
+        <v>14014300</v>
+      </c>
+      <c r="G54" s="3">
+        <v>13768600</v>
+      </c>
+      <c r="H54" s="3">
         <v>14632500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>14445500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>15985100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>16633700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>18704700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>18824900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>21821500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>21206400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>25488000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>26909500</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2724,12 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,218 +2743,294 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1009600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>994300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1169300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1148800</v>
+      </c>
+      <c r="H57" s="3">
         <v>1263100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>1247000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>1506900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>1568000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>1770500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>1781800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>1901200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>1847600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>1681500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>1775200</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>556000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>547600</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1406200</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1381500</v>
+      </c>
+      <c r="H58" s="3">
         <v>975700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>963300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>1139100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>1185300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>826700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>832000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>1609300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>1563900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>4213600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>4448600</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3153000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3105200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3145600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>3090500</v>
+      </c>
+      <c r="H59" s="3">
         <v>3582000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>3536200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>4313800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>4488800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>6084700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>6123800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>7926500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>7703000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>9108300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>9616300</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4718600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4647000</v>
+      </c>
+      <c r="F60" s="3">
+        <v>5721000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>5620700</v>
+      </c>
+      <c r="H60" s="3">
         <v>5820800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>5746500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>6959700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>7242100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>8681800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>8737600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>11437000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>11114600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>15003400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>15840200</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2553400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2514700</v>
+      </c>
+      <c r="F61" s="3">
+        <v>2155400</v>
+      </c>
+      <c r="G61" s="3">
+        <v>2117600</v>
+      </c>
+      <c r="H61" s="3">
         <v>2403400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>2372700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>2624300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>2730700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>2807500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>2825500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>3221700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>3231300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>3420300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>3611100</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>85700</v>
+      </c>
+      <c r="F62" s="3">
+        <v>111000</v>
+      </c>
+      <c r="G62" s="3">
+        <v>109100</v>
+      </c>
+      <c r="H62" s="3">
         <v>426300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>420800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>484500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>504200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>763600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>768500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>423200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>310800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>91700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>96900</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +3064,20 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +3111,20 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +3158,67 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7929600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7809300</v>
+      </c>
+      <c r="F66" s="3">
+        <v>8542100</v>
+      </c>
+      <c r="G66" s="3">
+        <v>8392400</v>
+      </c>
+      <c r="H66" s="3">
         <v>9231200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>9113300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>10614500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>11045100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>12802200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>12884500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>15653200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>15211900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>19125300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>20191900</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +3232,12 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +3271,20 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +3318,20 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +3365,20 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +3412,67 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4019000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3958000</v>
+      </c>
+      <c r="F72" s="3">
+        <v>3939900</v>
+      </c>
+      <c r="G72" s="3">
+        <v>3870800</v>
+      </c>
+      <c r="H72" s="3">
         <v>3879600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>3830100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>3752400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>3904600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>4173500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>4200300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>4342300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>4219900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>4523700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>4776000</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +3506,20 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3553,20 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3600,67 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4764700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4692400</v>
+      </c>
+      <c r="F76" s="3">
+        <v>4710300</v>
+      </c>
+      <c r="G76" s="3">
+        <v>4627700</v>
+      </c>
+      <c r="H76" s="3">
         <v>4430800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>4374200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>4213700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>4384600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>4616300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>4646000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>4840600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>4704100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>4969600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>5246800</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,48 +3694,72 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3014,8 +3793,20 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3820,59 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>8800</v>
+      </c>
+      <c r="G83" s="3">
+        <v>9200</v>
+      </c>
+      <c r="H83" s="3">
         <v>9700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="I83" s="3">
         <v>9800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="J83" s="3">
         <v>9900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="K83" s="3">
         <v>9600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>10500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>11100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>11200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>10900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>11600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3906,20 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3953,20 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +4000,20 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +4047,20 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +4094,67 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F89" s="3">
+        <v>98400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>96700</v>
+      </c>
+      <c r="H89" s="3">
         <v>-43000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>-42400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>174500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>181600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>73400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>71300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>237100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>250400</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +4168,59 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="I91" s="3">
         <v>-2100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
         <v>-3700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-2800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-2800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-2700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-3900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +4254,20 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +4301,67 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F94" s="3">
+        <v>66600</v>
+      </c>
+      <c r="G94" s="3">
+        <v>65400</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>18700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>19400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>26400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>26600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>60400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>58700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>33400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>35300</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,16 +4375,20 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>7700</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>4</v>
@@ -3479,8 +4414,20 @@
       <c r="M96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +4461,20 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +4508,20 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +4555,157 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-92600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-91200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-232400</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-228300</v>
+      </c>
+      <c r="H100" s="3">
         <v>-91600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>-90400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>-221100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-230100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-190200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-191400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-584200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-567800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-355700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-375500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="J101" s="3">
         <v>-6900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="K101" s="3">
         <v>-6700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="M101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="N101" s="3">
         <v>13400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="O101" s="3">
         <v>13000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-115300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-113500</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-75900</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-74500</v>
+      </c>
+      <c r="H102" s="3">
         <v>-127900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>-126300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>-30900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>-32200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>-162700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>-163800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-457300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>-444400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-83000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>-87600</v>
       </c>
     </row>
